--- a/Tools/Luban/DataTables/Datas/障碍物_Obstacle.xlsx
+++ b/Tools/Luban/DataTables/Datas/障碍物_Obstacle.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="obstacle" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="obstacle" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Tools/Luban/DataTables/Datas/障碍物_Obstacle.xlsx
+++ b/Tools/Luban/DataTables/Datas/障碍物_Obstacle.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +484,11 @@
           <t>dropQuantity</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>iconSprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -515,6 +521,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -545,6 +556,11 @@
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>掉落数量</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>世界sprite名</t>
         </is>
       </c>
     </row>
@@ -567,6 +583,11 @@
       <c r="F4" t="n">
         <v>2</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SL_Deco_c2_r0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -587,6 +608,11 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SL_Deco_c6_r3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -607,6 +633,86 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SL_Tree_c4_r5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>obstacle_4</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SL_Deco_c4_r0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>obstacle_5</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SL_Deco_c8_r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>obstacle_6</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SL_Tree_c6_r5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
